--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487558_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487558_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2333</v>
+        <v>-0.011</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5927</v>
+        <v>1.3218</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3594</v>
+        <v>-1.3327</v>
       </c>
       <c r="G2" t="n">
         <v>-2.8545</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3968</v>
+        <v>1.1526</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8973</v>
+        <v>0.6264</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4995</v>
+        <v>0.5262</v>
       </c>
       <c r="V2" t="n">
         <v>0.1242</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3889</v>
+        <v>-0.3295</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7806</v>
+        <v>-0.7212</v>
       </c>
       <c r="F3" t="n">
         <v>0.3917</v>
@@ -688,10 +688,10 @@
         <v>0.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5576</v>
+        <v>-0.4715</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8994</v>
+        <v>-0.84</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3418</v>
+        <v>0.3685</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7295</v>
@@ -766,13 +766,13 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2198</v>
+        <v>-0.1337</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2376</v>
+        <v>-0.1782</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>I. FERNANDEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7089</v>
+        <v>-0.7351</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6468</v>
+        <v>0.8218</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0621</v>
+        <v>-1.557</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.1175</v>
+        <v>0.0188</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1776</v>
+        <v>-4.3771</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.2951</v>
+        <v>4.396</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3728</v>
+        <v>5.5166</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6253</v>
+        <v>-1.9294</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.9981</v>
+        <v>7.446</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7447</v>
+        <v>-5.4978</v>
       </c>
       <c r="N5" t="n">
         <v>-2.4477</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.297</v>
+        <v>-3.05</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9377</v>
+        <v>-5.8755</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7419</v>
+        <v>2.9377</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4952</v>
+        <v>0.9006</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6211</v>
+        <v>-0.0359</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8741</v>
+        <v>0.9365</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1093</v>
+        <v>1.2832</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0427</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
         <v>0.06660000000000001</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8433</v>
+        <v>-1.0972</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1184</v>
+        <v>-1.142</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.725</v>
+        <v>0.0448</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4401</v>
+        <v>-4.1175</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3489</v>
+        <v>1.1776</v>
       </c>
       <c r="I6" t="n">
-        <v>0.789</v>
+        <v>-5.2951</v>
       </c>
       <c r="J6" t="n">
-        <v>5.2629</v>
+        <v>-0.3728</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4187</v>
+        <v>3.6253</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8443</v>
+        <v>-3.9981</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.8228</v>
+        <v>-3.7447</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7676</v>
+        <v>-2.4477</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.0552</v>
+        <v>-1.297</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.1958</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-2.9377</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-5.8755</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.9377</v>
+        <v>2.7419</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5877</v>
+        <v>1.1069</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5058</v>
+        <v>0.1259</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0935</v>
+        <v>0.981</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06660000000000001</v>
+        <v>2.1093</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.0427</v>
       </c>
       <c r="X6" t="n">
         <v>0.06660000000000001</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MUÑOZ</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2051</v>
+        <v>-1.1002</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5679</v>
+        <v>-0.402</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6372</v>
+        <v>-0.6982</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0188</v>
+        <v>0.4401</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.3771</v>
+        <v>-0.3489</v>
       </c>
       <c r="I7" t="n">
-        <v>4.396</v>
+        <v>0.789</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5166</v>
+        <v>5.2629</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9294</v>
+        <v>1.4187</v>
       </c>
       <c r="L7" t="n">
-        <v>7.446</v>
+        <v>3.8443</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.4978</v>
+        <v>-4.8228</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4477</v>
+        <v>-1.7676</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.05</v>
+        <v>-3.0552</v>
       </c>
       <c r="P7" t="n">
         <v>-2.9377</v>
@@ -1000,19 +1000,19 @@
         <v>2.9377</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5694</v>
+        <v>1.3308</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4256</v>
+        <v>0.2105</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8563</v>
+        <v>1.1203</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2832</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0.06660000000000001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.3827</v>
+        <v>-4.1268</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7441</v>
+        <v>-2.4034</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6385</v>
+        <v>-1.7234</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.4045</v>
+        <v>-4.8845</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9051</v>
+        <v>-2.0855</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4994</v>
+        <v>-2.799</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8256</v>
+        <v>-2.3211</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5427</v>
+        <v>-0.997</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2829</v>
+        <v>-1.3241</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.2301</v>
+        <v>-2.5634</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.4477</v>
+        <v>-1.0885</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.7823</v>
+        <v>-1.475</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.3294</v>
+        <v>0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.8755</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.546</v>
+        <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6764</v>
+        <v>-0.2216</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4221</v>
+        <v>-0.0823</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2543</v>
+        <v>-0.1392</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6749000000000001</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>A. BLANCO BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8375</v>
+        <v>-5.142</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0339</v>
+        <v>-4.4211</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8036</v>
+        <v>-0.7208</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.8845</v>
+        <v>-6.4513</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0855</v>
+        <v>-3.7282</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.799</v>
+        <v>-2.723</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3211</v>
+        <v>-3.492</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.997</v>
+        <v>-1.6878</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3241</v>
+        <v>-1.8042</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5634</v>
+        <v>-2.9593</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0885</v>
+        <v>-2.0405</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.475</v>
+        <v>-0.9188</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9792</v>
+        <v>2.1543</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9323</v>
+        <v>0.4671</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7128</v>
+        <v>-0.2253</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2194</v>
+        <v>0.6924</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BLANCO BLANCO</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1701</v>
+        <v>-5.2535</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5829</v>
+        <v>-3.4011</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-1.8524</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.4513</v>
+        <v>-4.4045</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.7282</v>
+        <v>-1.9051</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.723</v>
+        <v>-2.4994</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.492</v>
+        <v>0.8256</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.6878</v>
+        <v>0.5427</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8042</v>
+        <v>0.2829</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9593</v>
+        <v>-5.2301</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.0405</v>
+        <v>-2.4477</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9188</v>
+        <v>-2.7823</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1751</v>
+        <v>-3.3294</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-5.8755</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1543</v>
+        <v>2.546</v>
       </c>
       <c r="S10" t="n">
-        <v>0.439</v>
+        <v>1.8056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.387</v>
+        <v>0.7652</v>
       </c>
       <c r="U10" t="n">
-        <v>0.826</v>
+        <v>1.0404</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3329</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0.8837</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6083</v>
+        <v>-0.2088</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.8608</v>
+        <v>-18.2668</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.7813</v>
+        <v>-11.1872</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.079499999999999</v>
+        <v>-7.0795</v>
       </c>
       <c r="G11" t="n">
         <v>-23.6447</v>
@@ -1285,13 +1285,13 @@
         <v>-11.3644</v>
       </c>
       <c r="J11" t="n">
-        <v>4.182700000000001</v>
+        <v>4.1827</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9792000000000003</v>
+        <v>0.9792000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>3.203600000000001</v>
+        <v>3.2036</v>
       </c>
       <c r="M11" t="n">
         <v>-27.8274</v>
@@ -1312,13 +1312,13 @@
         <v>16.647</v>
       </c>
       <c r="S11" t="n">
-        <v>5.754799999999999</v>
+        <v>6.3489</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5528999999999997</v>
+        <v>1.1469</v>
       </c>
       <c r="U11" t="n">
-        <v>5.202099999999999</v>
+        <v>5.202199999999999</v>
       </c>
       <c r="V11" t="n">
         <v>3.9253</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.3041</v>
+        <v>9.562200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>6.8328</v>
+        <v>7.0375</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4713</v>
+        <v>2.5248</v>
       </c>
       <c r="G12" t="n">
         <v>8.8102</v>
@@ -1390,13 +1390,13 @@
         <v>1.9585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8183</v>
+        <v>-0.5602</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7722</v>
+        <v>-0.5676</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0461</v>
+        <v>0.0074</v>
       </c>
       <c r="V12" t="n">
         <v>0.3329</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8502</v>
+        <v>4.1442</v>
       </c>
       <c r="E13" t="n">
         <v>4.2927</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4425</v>
+        <v>-0.1485</v>
       </c>
       <c r="G13" t="n">
         <v>6.6423</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1043</v>
+        <v>-0.8103</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2682</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8361</v>
+        <v>-0.5421</v>
       </c>
       <c r="V13" t="n">
         <v>-1.492</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.609</v>
+        <v>3.1508</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4808</v>
+        <v>0.9691</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1282</v>
+        <v>2.1817</v>
       </c>
       <c r="G14" t="n">
         <v>1.2056</v>
@@ -1546,13 +1546,13 @@
         <v>3.5253</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1426</v>
+        <v>-0.6008</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0612</v>
+        <v>-0.5729</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0814</v>
+        <v>-0.0279</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1401</v>
+        <v>3.0775</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2571</v>
+        <v>1.4618</v>
       </c>
       <c r="F15" t="n">
-        <v>1.883</v>
+        <v>1.6157</v>
       </c>
       <c r="G15" t="n">
         <v>4.0517</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0498</v>
+        <v>-1.1125</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8316</v>
+        <v>-0.627</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2182</v>
+        <v>-0.4855</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0576</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2861</v>
+        <v>2.2418</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9469</v>
+        <v>1.4102</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3392</v>
+        <v>0.8316</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1461</v>
+        <v>0.5843</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5543</v>
+        <v>1.2205</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5918</v>
+        <v>-0.6363</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7191</v>
+        <v>1.2437</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1429</v>
+        <v>1.082</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5762</v>
+        <v>0.1617</v>
       </c>
       <c r="M16" t="n">
-        <v>0.427</v>
+        <v>-0.6594</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4114</v>
+        <v>0.1385</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0156</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5524</v>
+        <v>0.0907</v>
       </c>
       <c r="T16" t="n">
-        <v>0.207</v>
+        <v>-0.1088</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3454</v>
+        <v>0.1995</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6083</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9615</v>
+        <v>1.6362</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1032</v>
+        <v>0.5375</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8583</v>
+        <v>1.0986</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5843</v>
+        <v>2.1461</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2205</v>
+        <v>0.5543</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6363</v>
+        <v>1.5918</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2437</v>
+        <v>1.7191</v>
       </c>
       <c r="K17" t="n">
-        <v>1.082</v>
+        <v>0.1429</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1617</v>
+        <v>1.5762</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6594</v>
+        <v>0.427</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1385</v>
+        <v>0.4114</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7979000000000001</v>
+        <v>0.0156</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1896</v>
+        <v>-0.0975</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4158</v>
+        <v>-0.2023</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2263</v>
+        <v>0.1048</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5739</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>0.5735</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0005</v>
+        <v>0.1074</v>
       </c>
       <c r="G18" t="n">
         <v>1.111</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0713</v>
+        <v>0.1782</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1307</v>
+        <v>0.2376</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2227</v>
+        <v>0.2449</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8338</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0565</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.4303</v>
@@ -1936,13 +1936,13 @@
         <v>1.7626</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0117</v>
+        <v>0.0104</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7722</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7605</v>
+        <v>0.6803</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3094</v>
+        <v>-0.2338</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0026</v>
+        <v>0.105</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.312</v>
+        <v>-0.3387</v>
       </c>
       <c r="G20" t="n">
         <v>1.6079</v>
@@ -2014,13 +2014,13 @@
         <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.347</v>
+        <v>-1.2714</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.891</v>
+        <v>-0.7887</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.456</v>
+        <v>-0.4827</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5495</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. NIETO FONTAIÑA</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.246</v>
+        <v>-1.1419</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7005</v>
+        <v>-3.6321</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4545</v>
+        <v>2.4902</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3202</v>
+        <v>-0.6469</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0892</v>
+        <v>1.9211</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4093</v>
+        <v>-2.568</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.0698</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0204</v>
+        <v>1.9836</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6822</v>
+        <v>-2.0534</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3416</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0687</v>
+        <v>-0.0625</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2729</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.1336</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0535</v>
+        <v>-1.0238</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0594</v>
+        <v>-0.6246</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1129</v>
+        <v>-0.3992</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>S. NIETO FONTAIÑA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.329</v>
+        <v>-1.1658</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6321</v>
+        <v>-1.7005</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3031</v>
+        <v>0.5347</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6469</v>
+        <v>-0.3202</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9211</v>
+        <v>0.0892</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.568</v>
+        <v>-0.4093</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0698</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9836</v>
+        <v>0.0204</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0534</v>
+        <v>-0.6822</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5770999999999999</v>
+        <v>0.3416</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0625</v>
+        <v>0.0687</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5145999999999999</v>
+        <v>0.2729</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1336</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2109</v>
+        <v>0.1337</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6246</v>
+        <v>-0.0594</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5863</v>
+        <v>0.1931</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2024</v>
+        <v>-3.3361</v>
       </c>
       <c r="E23" t="n">
         <v>-3.2437</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0412</v>
+        <v>-0.0924</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9775</v>
@@ -2248,13 +2248,13 @@
         <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5578</v>
+        <v>-0.6915</v>
       </c>
       <c r="T23" t="n">
         <v>-0.6534</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0956</v>
+        <v>-0.0381</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2754</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.8608</v>
+        <v>18.8609</v>
       </c>
       <c r="E24" t="n">
-        <v>7.079499999999998</v>
+        <v>7.079599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>11.7813</v>
+        <v>11.7814</v>
       </c>
       <c r="G24" t="n">
         <v>23.64480000000001</v>
@@ -2308,7 +2308,7 @@
         <v>14.568</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.1828</v>
+        <v>-4.182799999999999</v>
       </c>
       <c r="N24" t="n">
         <v>-0.9792</v>
@@ -2326,13 +2326,13 @@
         <v>21.5434</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.7548</v>
+        <v>-5.755000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.202</v>
+        <v>-5.202199999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5527000000000001</v>
+        <v>-0.5528000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9253</v>
